--- a/KURIKULUM2026_REVISI/014_ANALISIS_KRITIS_PEMANGKASAN_SKS_TEORI_SEM4_SEM5.xlsx
+++ b/KURIKULUM2026_REVISI/014_ANALISIS_KRITIS_PEMANGKASAN_SKS_TEORI_SEM4_SEM5.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>`STI-404`</t>
+          <t>`STI-417`</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>`STI-405`</t>
+          <t>`STI-418`</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>`STI-506`</t>
+          <t>`STI-523`</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
